--- a/sample-data/perfect-submission/Heartland_Express_Vehicle_Schedule.xlsx
+++ b/sample-data/perfect-submission/Heartland_Express_Vehicle_Schedule.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vehicle Schedule" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Vehicle Schedule" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,11 +457,11 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
@@ -469,7 +469,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HEARTLAND EXPRESS TRUCKING LLC — VEHICLE / EQUIPMENT SCHEDULE</t>
+          <t>HEARTLAND EXPRESS TRUCKING LLC - VEHICLE / EQUIPMENT SCHEDULE</t>
         </is>
       </c>
     </row>
@@ -525,8 +525,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>1</v>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>T-101</t>
+        </is>
       </c>
       <c r="B5" s="5" t="n">
         <v>2022</v>
@@ -558,8 +560,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>2</v>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>T-102</t>
+        </is>
       </c>
       <c r="B6" s="5" t="n">
         <v>2021</v>
@@ -591,8 +595,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>T-103</t>
+        </is>
       </c>
       <c r="B7" s="5" t="n">
         <v>2023</v>
@@ -624,8 +630,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>4</v>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>T-104</t>
+        </is>
       </c>
       <c r="B8" s="5" t="n">
         <v>2022</v>
@@ -657,8 +665,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>5</v>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>T-105</t>
+        </is>
       </c>
       <c r="B9" s="5" t="n">
         <v>2020</v>
@@ -730,8 +740,10 @@
       <c r="G12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>1</v>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>TR-201</t>
+        </is>
       </c>
       <c r="B13" s="5" t="n">
         <v>2021</v>
@@ -743,12 +755,12 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>1GRAA0622NB123456</t>
+          <t>1GRAA0622MB123456</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Dry Van Trailer</t>
+          <t>Dry Van</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -756,11 +768,12 @@
           <t>53 ft</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>2</v>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>TR-202</t>
+        </is>
       </c>
       <c r="B14" s="5" t="n">
         <v>2022</v>
@@ -772,12 +785,12 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>1UYVS2530NM234567</t>
+          <t>1UYVS2530NM654321</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Dry Van Trailer</t>
+          <t>Dry Van</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -785,28 +798,29 @@
           <t>53 ft</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>3</v>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>TR-203</t>
+        </is>
       </c>
       <c r="B15" s="5" t="n">
         <v>2020</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Wabash National</t>
+          <t>Wabash National DuraPlate</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>1JJV532B8NL345678</t>
+          <t>1JJV532B5ML987654</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Dry Van Trailer</t>
+          <t>Dry Van</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -814,28 +828,29 @@
           <t>53 ft</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
-        <v>4</v>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>TR-204</t>
+        </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Great Dane Champion</t>
+          <t>Hyundai Translead</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>1GRAA8826NN678901</t>
+          <t>3H3V532C6PT246813</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Reefer Trailer</t>
+          <t>Reefer</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -843,7 +858,6 @@
           <t>53 ft</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
